--- a/generated/spreadsheet/verbose/advertising-advertising-verbose.xlsx
+++ b/generated/spreadsheet/verbose/advertising-advertising-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N96"/>
+  <dimension ref="A1:N95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -642,12 +642,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>application-sub-type</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>submission-date</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>modules</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -786,21 +786,29 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -844,19 +852,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -900,19 +908,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -922,7 +930,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -956,29 +964,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1012,24 +1020,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1068,29 +1076,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>base64-content</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1150,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>base64-content</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1154,7 +1170,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1198,17 +1214,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1218,7 +1234,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1262,22 +1278,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>file-size</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1306,37 +1322,29 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>file-size</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1346,7 +1354,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1380,19 +1388,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1436,99 +1444,83 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>transactions</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Advertisement location</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>advert-location</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Where the advertisement being applied to be built will be located</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>is-advert-in-place</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>fee</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>transactions</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>Is advert in place</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>Whether the advertisement is already in place</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Advertisement location</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>advert-location</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Where the advertisement being applied to be built will be located</t>
@@ -1536,12 +1528,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>is-advert-in-place</t>
+          <t>advert-placed-date</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Is advert in place</t>
+          <t>Advert placed date</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
@@ -1552,17 +1544,17 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Whether the advertisement is already in place</t>
+          <t>Date when the advertisement was placed (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1568,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>advert-placed-date</t>
+          <t>is-replacement-advert</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Advert placed date</t>
+          <t>Is replacement advert</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
@@ -1592,17 +1584,17 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Date when the advertisement was placed (YYYY-MM-DD format)</t>
+          <t>Whether this is a replacement advertisement</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1616,28 +1608,36 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>is-replacement-advert</t>
+          <t>document-reference</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Is replacement advert</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
+          <t>Document reference[]</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Whether this is a replacement advertisement</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1656,36 +1656,28 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>document-reference</t>
+          <t>is-advert-overhanging</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Document reference[]</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Is advert overhanging</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Whether the advertisement will project over a footpath or other public highway</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -1695,21 +1687,29 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Advert period</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>advert-period</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Where the advertisement being applied to be built will be located</t>
+          <t>How long the proposed advertisement will be shown.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>is-advert-overhanging</t>
+          <t>advert-start-date</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Is advert overhanging</t>
+          <t>Advert start date</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
@@ -1720,12 +1720,12 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Whether the advertisement will project over a footpath or other public highway</t>
+          <t>The start of the time period that consent to advertisement is sought</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -1735,16 +1735,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Advert period</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>advert-period</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>How long the proposed advertisement will be shown.</t>
@@ -1752,12 +1744,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>advert-start-date</t>
+          <t>advert-end-date</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Advert start date</t>
+          <t>Advert end date</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
@@ -1768,7 +1760,7 @@
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>The start of the time period that consent to advertisement is sought</t>
+          <t>The end of the time period that consent to advertisement is sought</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1783,21 +1775,29 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="2" t="n"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Advertisement types</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>advertisement-types</t>
+        </is>
+      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>How long the proposed advertisement will be shown.</t>
+          <t>What type of advertisements are proposed and how many there will be.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>advert-end-date</t>
+          <t>advertisement-proposal-description</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Advert end date</t>
+          <t>Advertisement proposal description</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
@@ -1808,12 +1808,12 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>The end of the time period that consent to advertisement is sought</t>
+          <t>Description of the advertisement proposal</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -1823,16 +1823,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Advertisement types</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>advertisement-types</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>What type of advertisements are proposed and how many there will be.</t>
@@ -1840,28 +1832,36 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>advertisement-proposal-description</t>
+          <t>advertisement-proposal-type</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Advertisement proposal description</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
+          <t>Advertisement proposal type[]</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>advertisement-type</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Advertisement type</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Description of the advertisement proposal</t>
+          <t>One of the advertisement-types or other</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>advertisement-type</t>
+          <t>advertisement-count</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Advertisement type</t>
+          <t>Advertisement count</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -1904,12 +1904,12 @@
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>One of the advertisement-types or other</t>
+          <t>Number of this type of advertisement</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>advertisement-count</t>
+          <t>advertisement-other-description</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Advertisement count</t>
+          <t>Advertisement other description</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -1952,55 +1952,55 @@
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Number of this type of advertisement</t>
+          <t>Details required if other advertisement type is selected</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>What type of advertisements are proposed and how many there will be.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>advertisement-proposal-type</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Advertisement proposal type[]</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>advertisement-other-description</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Advertisement other description</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Details required if other advertisement type is selected</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2010,21 +2010,13 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -2032,23 +2024,31 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -2082,21 +2082,29 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2106,7 +2114,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2140,24 +2148,24 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2167,8 +2175,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n"/>
-      <c r="B34" s="2" t="n"/>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -2176,63 +2192,47 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -2250,21 +2250,29 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -2274,7 +2282,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2308,19 +2316,19 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2330,7 +2338,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2364,19 +2372,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2420,19 +2428,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2476,19 +2484,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2498,7 +2506,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2522,29 +2530,21 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>user-role</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -2592,12 +2592,12 @@
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -2607,64 +2607,56 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="n"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>user-role</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2672,23 +2664,31 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -2722,21 +2722,29 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -2746,7 +2754,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2780,24 +2788,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -2807,72 +2815,64 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n"/>
-      <c r="B46" s="2" t="n"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2890,21 +2890,29 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -2914,7 +2922,7 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2948,19 +2956,19 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -2970,7 +2978,7 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3004,19 +3012,19 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -3060,19 +3068,19 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -3116,19 +3124,19 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -3138,53 +3146,45 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n"/>
-      <c r="B52" s="2" t="n"/>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>National requirement types[]</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -3194,34 +3194,34 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Community consultation</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>checklist</t>
+          <t>community-consultation</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>What community consultation activities have taken place as part of the application</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>have-consulted</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Have consulted</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -3232,12 +3232,12 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Whether community consultation has been carried out</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -3247,16 +3247,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Community consultation</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>community-consultation</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>What community consultation activities have taken place as part of the application</t>
@@ -3264,12 +3256,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>have-consulted</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Have consulted</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
@@ -3280,36 +3272,44 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Whether community consultation has been carried out</t>
+          <t>Provide details of the community consultation</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n"/>
-      <c r="B55" s="2" t="n"/>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>What community consultation activities have taken place as part of the application</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
@@ -3320,31 +3320,23 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Provide details of the community consultation</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -3352,12 +3344,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>conflict-person-name</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Conflict person name</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3368,17 +3360,17 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3392,12 +3384,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>conflict-person-name</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -3408,7 +3400,7 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -3423,21 +3415,29 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="2" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Interest in land</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>interest-in-land</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Whether the applicant owns or has permission to use the land where the proposed advertisement will be placed</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>applicant-owns-land</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Applicant owns land</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -3448,31 +3448,23 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>True or False indicating whether the applicant owns the land where the advertisement will be displayed</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Interest in land</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>interest-in-land</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Whether the applicant owns or has permission to use the land where the proposed advertisement will be placed</t>
@@ -3480,12 +3472,12 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>applicant-owns-land</t>
+          <t>permission-obtained</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Applicant owns land</t>
+          <t>Permission obtained</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
@@ -3496,7 +3488,7 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>True or False indicating whether the applicant owns the land where the advertisement will be displayed</t>
+          <t>True or False indicating whether permission of the owner for the display of an advertisement has been obtained</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -3506,7 +3498,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3520,12 +3512,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>permission-obtained</t>
+          <t>permission-not-obtained-details</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Permission obtained</t>
+          <t>Permission not obtained details</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
@@ -3536,12 +3528,12 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>True or False indicating whether permission of the owner for the display of an advertisement has been obtained</t>
+          <t>Details explaining why permission from the land owner has not been obtained for the advertisement display</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -3551,21 +3543,29 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="2" t="n"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Whether the applicant owns or has permission to use the land where the proposed advertisement will be placed</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>permission-not-obtained-details</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Permission not obtained details</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -3576,7 +3576,7 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Details explaining why permission from the land owner has not been obtained for the advertisement display</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -3586,21 +3586,13 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -3608,12 +3600,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
@@ -3624,12 +3616,12 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -3648,12 +3640,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
@@ -3664,12 +3656,12 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -3679,21 +3671,29 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
@@ -3704,12 +3704,12 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3719,16 +3719,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -3736,12 +3728,12 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -3752,17 +3744,17 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3776,12 +3768,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -3792,7 +3784,7 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -3816,12 +3808,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
@@ -3832,7 +3824,7 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -3856,12 +3848,12 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
@@ -3872,7 +3864,7 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -3887,37 +3879,53 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n"/>
-      <c r="B69" s="2" t="n"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Proposed advert details</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>proposed-advert-details</t>
+        </is>
+      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Details of the proposed advertisements such as their size and how they are made</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>advertisements</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
+          <t>Advertisements[]</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>height-from-ground</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Height from ground</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Height, in metres, from ground to the base of the advertisement</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -3927,16 +3935,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Proposed advert details</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>proposed-advert-details</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="n"/>
+      <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Details of the proposed advertisements such as their size and how they are made</t>
@@ -3954,12 +3954,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>height-from-ground</t>
+          <t>height</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Height from ground</t>
+          <t>Height</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -3968,7 +3968,7 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Height, in metres, from ground to the base of the advertisement</t>
+          <t>Height, in metres, of dimensions of advertisement</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>height</t>
+          <t>width</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Height</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -4016,7 +4016,7 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Height, in metres, of dimensions of advertisement</t>
+          <t>Width of dimensions of advertisement</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>width</t>
+          <t>depth</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Depth</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4064,7 +4064,7 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Width of dimensions of advertisement</t>
+          <t>Depth, in metres, of dimensions of advertisement</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -4098,12 +4098,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>depth</t>
+          <t>symbol-height-max</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Depth</t>
+          <t>Symbol height max</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -4112,7 +4112,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Depth, in metres, of dimensions of advertisement</t>
+          <t>Maximum height, in metres, of any individual letters or symbols</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -4146,12 +4146,12 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>symbol-height-max</t>
+          <t>colour</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Symbol height max</t>
+          <t>Colour</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -4160,12 +4160,12 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Maximum height, in metres, of any individual letters or symbols</t>
+          <t>Colour of proposed sign</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>colour</t>
+          <t>materials</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Colour</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -4208,7 +4208,7 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Colour of proposed sign</t>
+          <t>Materials of proposed sign</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>materials</t>
+          <t>max-projection</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Max projection</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -4256,12 +4256,12 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Materials of proposed sign</t>
+          <t>Maximum projection, in metres, of the advertisement from the face of the building</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>max-projection</t>
+          <t>illuminated</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Max projection</t>
+          <t>Illuminated</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -4304,12 +4304,12 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Maximum projection, in metres, of the advertisement from the face of the building</t>
+          <t>Will the sign(s) be illuminated?</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>illuminated</t>
+          <t>illumination-method</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Illuminated</t>
+          <t>Illumination method</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -4352,12 +4352,12 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Will the sign(s) be illuminated?</t>
+          <t>Method of illumination for the advertisement</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>illumination-method</t>
+          <t>illuminance-level</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Illumination method</t>
+          <t>Illuminance level</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -4400,12 +4400,12 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Method of illumination for the advertisement</t>
+          <t>Level of illuminance for the advertisement</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>illuminance-level</t>
+          <t>illumination-type</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Illuminance level</t>
+          <t>Illumination type</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -4448,12 +4448,12 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Level of illuminance for the advertisement</t>
+          <t>Type of illumination (static or intermittent)</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -4463,31 +4463,39 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n"/>
-      <c r="B81" s="2" t="n"/>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Details of the proposed advertisements such as their size and how they are made</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>advertisements</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Advertisements[]</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>illumination-type</t>
+          <t>site-boundary</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Illumination type</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
@@ -4496,12 +4504,12 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Type of illumination (static or intermittent)</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -4511,16 +4519,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -4538,12 +4538,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -4552,12 +4552,12 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -4600,7 +4600,7 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -4648,12 +4648,12 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -4696,7 +4696,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -4744,7 +4744,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
@@ -4792,7 +4792,7 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
@@ -4840,12 +4840,12 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>uprns</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
@@ -4888,7 +4888,7 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -4903,64 +4903,56 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n"/>
-      <c r="B90" s="2" t="n"/>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>uprns</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -4968,12 +4960,12 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -4984,12 +4976,12 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -5008,12 +5000,12 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
@@ -5024,17 +5016,17 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5048,23 +5040,31 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>fullname</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
@@ -5112,7 +5112,7 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
@@ -5160,7 +5160,7 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -5169,54 +5169,6 @@
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n"/>
-      <c r="B96" s="2" t="n"/>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>other-contact</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-      <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N96" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -5224,40 +5176,40 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="A35:A42"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="B35:B42"/>
-    <mergeCell ref="A53"/>
-    <mergeCell ref="B91:B96"/>
-    <mergeCell ref="B65:B69"/>
-    <mergeCell ref="B82:B90"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="B47:B52"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="B43:B46"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B20:B24"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B59:B61"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="A70:A81"/>
-    <mergeCell ref="A91:A96"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="A47:A52"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="B70:B81"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="B53"/>
-    <mergeCell ref="A65:A69"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A34:A41"/>
+    <mergeCell ref="A52"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B46:B51"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B64:B68"/>
+    <mergeCell ref="B90:B95"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="A69:A80"/>
+    <mergeCell ref="A19:A23"/>
+    <mergeCell ref="A81:A89"/>
+    <mergeCell ref="A64:A68"/>
+    <mergeCell ref="A90:A95"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="B52"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="B81:B89"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B34:B41"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B69:B80"/>
+    <mergeCell ref="A55:A57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/advertising-advertising-verbose.xlsx
+++ b/generated/spreadsheet/verbose/advertising-advertising-verbose.xlsx
@@ -433,7 +433,7 @@
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="72" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
     <col width="33" customWidth="1" min="7" max="7"/>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>advertisement-proposal-description</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
